--- a/erp-server/erp-server-wms/src/main/resources/excel/inventory_area.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/inventory_area.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <r>
       <rPr>
@@ -111,9 +111,6 @@
     <t>仓库名称</t>
   </si>
   <si>
-    <t>仓位名称</t>
-  </si>
-  <si>
     <t>实际库存</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
-  </si>
-  <si>
-    <t>{.warehouseLocationName}</t>
   </si>
   <si>
     <t>{.realQty}</t>
@@ -1116,7 +1110,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -1126,12 +1120,12 @@
     <col min="5" max="5" width="21.375" customWidth="1"/>
     <col min="6" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="7" width="21.25" customWidth="1"/>
-    <col min="8" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="17.25" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1162,43 +1156,37 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
